--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486800_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486800_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.639</v>
+        <v>3.6142</v>
       </c>
       <c r="E2" t="n">
         <v>3.1075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5315</v>
+        <v>0.5067</v>
       </c>
       <c r="G2" t="n">
         <v>1.4927</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.182</v>
+        <v>-0.2068</v>
       </c>
       <c r="T2" t="n">
         <v>0.3859</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5679</v>
+        <v>-0.5927</v>
       </c>
       <c r="V2" t="n">
         <v>1.5559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1036</v>
+        <v>3.538</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7122</v>
+        <v>4.0225</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6086</v>
+        <v>-0.4845</v>
       </c>
       <c r="G3" t="n">
         <v>1.7832</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5444</v>
+        <v>-1.11</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1107</v>
+        <v>0.1995</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4337</v>
+        <v>-1.3096</v>
       </c>
       <c r="V3" t="n">
         <v>1.5133</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8415</v>
+        <v>2.1886</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0646</v>
+        <v>1.765</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7769</v>
+        <v>0.4236</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4215</v>
+        <v>1.8052</v>
       </c>
       <c r="H4" t="n">
-        <v>2.399</v>
+        <v>-0.5663</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0225</v>
+        <v>2.3715</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5059</v>
+        <v>2.3376</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7795</v>
+        <v>-0.1515</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7264</v>
+        <v>2.4891</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9156</v>
+        <v>-0.5324</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6195000000000001</v>
+        <v>-0.4148</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2961</v>
+        <v>-0.1176</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.4408</v>
+        <v>1.9308</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.7923</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8608</v>
+        <v>-1.2618</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3511</v>
+        <v>-0.5726</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4903</v>
+        <v>-0.6892</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.63</v>
+        <v>1.3708</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4547</v>
+        <v>1.0676</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1753</v>
+        <v>0.3032</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8052</v>
+        <v>0.7916</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5663</v>
+        <v>-0.6484</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3715</v>
+        <v>1.44</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3376</v>
+        <v>1.3435</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1515</v>
+        <v>0.0414</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4891</v>
+        <v>1.3022</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5324</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4148</v>
+        <v>-0.6898</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1176</v>
+        <v>0.1379</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8204</v>
+        <v>-0.1931</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8829</v>
+        <v>-0.2759</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9375</v>
+        <v>0.0828</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5671</v>
+        <v>0.9714</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0132</v>
+        <v>0.3927</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5787</v>
       </c>
       <c r="G6" t="n">
         <v>1.6751</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9266</v>
+        <v>0.3309</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1858</v>
+        <v>0.5652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2591</v>
+        <v>-0.2343</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2277</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3211</v>
+        <v>0.9434</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0676</v>
+        <v>-0.4079</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2535</v>
+        <v>1.3514</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7916</v>
+        <v>1.3641</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6484</v>
+        <v>-0.4897</v>
       </c>
       <c r="I7" t="n">
-        <v>1.44</v>
+        <v>1.8537</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3435</v>
+        <v>0.6747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0414</v>
+        <v>-0.6274</v>
       </c>
       <c r="L7" t="n">
         <v>1.3022</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.6893</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6898</v>
+        <v>0.1377</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1379</v>
+        <v>0.5516</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2428</v>
+        <v>-0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2759</v>
+        <v>-0.1173</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0331</v>
+        <v>-0.1102</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7407</v>
+        <v>0.6913</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5114</v>
+        <v>-0.7627</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2521</v>
+        <v>1.454</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3641</v>
+        <v>5.4215</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4897</v>
+        <v>2.399</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8537</v>
+        <v>3.0225</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6747</v>
+        <v>4.5059</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6274</v>
+        <v>1.7795</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3022</v>
+        <v>2.7264</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6893</v>
+        <v>0.9156</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1377</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5516</v>
+        <v>0.2961</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>-4.4408</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-5.7923</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4303</v>
+        <v>-0.2894</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2207</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2096</v>
+        <v>-0.8131</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.753</v>
+        <v>-0.7034</v>
       </c>
       <c r="E9" t="n">
         <v>-0.9102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1572</v>
+        <v>0.2068</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7585</v>
@@ -1156,13 +1156,13 @@
         <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1876</v>
+        <v>-0.138</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2207</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9591</v>
+        <v>-2.9799</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6663</v>
+        <v>-2.5628</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2929</v>
+        <v>-0.417</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3426</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1378</v>
+        <v>-0.1586</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0554</v>
+        <v>-0.0688</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0396</v>
+        <v>-3.9941</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1928</v>
+        <v>-2.2962</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8469</v>
+        <v>-1.6979</v>
       </c>
       <c r="G11" t="n">
         <v>1.6656</v>
@@ -1312,13 +1312,13 @@
         <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2798</v>
+        <v>-1.2342</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1383</v>
+        <v>-0.2417</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1415</v>
+        <v>-0.9925</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3709</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5472</v>
+        <v>-4.0964</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9683</v>
+        <v>-3.2443</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5789</v>
+        <v>-0.8521</v>
       </c>
       <c r="G12" t="n">
         <v>0.6863</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2022</v>
+        <v>-0.7514</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4691</v>
+        <v>0.2548</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7331</v>
+        <v>-1.0062</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.544099999999998</v>
+        <v>1.5439</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1708000000000007</v>
+        <v>0.1711999999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>1.373099999999999</v>
+        <v>1.3729</v>
       </c>
       <c r="G13" t="n">
         <v>13.5842</v>
@@ -1450,7 +1450,7 @@
         <v>8.6251</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6312</v>
+        <v>-2.631199999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-4.1456</v>
@@ -1468,13 +1468,13 @@
         <v>14.4808</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.2399</v>
+        <v>-5.24</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4112999999999999</v>
+        <v>0.4111000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.6511</v>
+        <v>-5.651</v>
       </c>
       <c r="V13" t="n">
         <v>-0.04269999999999985</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.354</v>
+        <v>2.5776</v>
       </c>
       <c r="E14" t="n">
-        <v>2.511</v>
+        <v>2.2688</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8431</v>
+        <v>0.3088</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.51</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5229</v>
+        <v>2.4971</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9872</v>
+        <v>-1.9261</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.1022</v>
+        <v>4.0277</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.4534</v>
+        <v>4.222</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6488</v>
+        <v>-0.1943</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4079</v>
+        <v>-3.4566</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-1.7249</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3384</v>
+        <v>-1.7318</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7377</v>
+        <v>1.1585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7031</v>
+        <v>3.2823</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4433</v>
+        <v>0.8481</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8955</v>
+        <v>0.365</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4521</v>
+        <v>0.4831</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6831</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.6831</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4257</v>
+        <v>2.1044</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2464</v>
+        <v>1.9362</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1793</v>
+        <v>0.1682</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0054</v>
@@ -1624,13 +1624,13 @@
         <v>3.4754</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5004</v>
+        <v>1.179</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4613</v>
+        <v>1.1511</v>
       </c>
       <c r="U15" t="n">
-        <v>0.039</v>
+        <v>0.0279</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6138</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9494</v>
+        <v>2.0896</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6151</v>
+        <v>0.9596</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6657</v>
+        <v>1.13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9458</v>
+        <v>-4.51</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5999</v>
+        <v>-2.5229</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3458</v>
+        <v>-1.9872</v>
       </c>
       <c r="J16" t="n">
-        <v>2.781</v>
+        <v>-3.1022</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0485</v>
+        <v>-2.4534</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7325</v>
+        <v>-0.6488</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8352</v>
+        <v>-1.4079</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4486</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3866</v>
+        <v>-1.3384</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>1.7377</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5446</v>
+        <v>2.7031</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4824</v>
+        <v>1.1789</v>
       </c>
       <c r="T16" t="n">
-        <v>1.958</v>
+        <v>1.3441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5244</v>
+        <v>-0.1652</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8995</v>
+        <v>3.6831</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.6831</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3158</v>
+        <v>1.4643</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1312</v>
+        <v>-0.4007</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1846</v>
+        <v>1.865</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5711000000000001</v>
+        <v>-1.1258</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4971</v>
+        <v>-2.0278</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9261</v>
+        <v>0.902</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0277</v>
+        <v>0.0133</v>
       </c>
       <c r="K17" t="n">
-        <v>4.222</v>
+        <v>-1.1307</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1943</v>
+        <v>1.144</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4566</v>
+        <v>-1.1391</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7249</v>
+        <v>-0.8972</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7318</v>
+        <v>-0.242</v>
       </c>
       <c r="P17" t="n">
         <v>1.1585</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1239</v>
+        <v>-1.1585</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2823</v>
+        <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4137</v>
+        <v>0.4896</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3589</v>
+        <v>0.359</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5942</v>
+        <v>0.5635</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3315</v>
+        <v>1.4774</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9258</v>
+        <v>-0.914</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1258</v>
+        <v>0.9458</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0278</v>
+        <v>0.5999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.902</v>
+        <v>0.3458</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0133</v>
+        <v>2.781</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1307</v>
+        <v>2.0485</v>
       </c>
       <c r="L18" t="n">
-        <v>1.144</v>
+        <v>0.7325</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1391</v>
+        <v>-1.8352</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8972</v>
+        <v>-1.4486</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.242</v>
+        <v>-0.3866</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3805</v>
+        <v>1.0964</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8002</v>
+        <v>0.8203</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4197</v>
+        <v>0.2761</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9421</v>
+        <v>-0.8995</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3282</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0499</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5871</v>
+        <v>-1.6905</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5373</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-2.546</v>
@@ -1936,13 +1936,13 @@
         <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>0.044</v>
+        <v>0.2275</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6342</v>
+        <v>0.5308</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.3033</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8374</v>
+        <v>-4.098</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2636</v>
+        <v>-2.5739</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5738</v>
+        <v>-1.5241</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8606</v>
@@ -2014,13 +2014,13 @@
         <v>2.8962</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6949</v>
+        <v>0.4343</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7995</v>
+        <v>0.4892</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1045</v>
+        <v>-0.0549</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5133</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2959</v>
+        <v>-4.6894</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6944</v>
+        <v>-3.3499</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6015</v>
+        <v>-1.3395</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0532</v>
@@ -2092,13 +2092,13 @@
         <v>3.2823</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1309</v>
+        <v>0.4757</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5244</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6065</v>
+        <v>-0.3444</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2703</v>
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5441</v>
+        <v>-0.8543999999999983</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3729</v>
+        <v>-1.373</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1709000000000002</v>
+        <v>0.5185</v>
       </c>
       <c r="G22" t="n">
         <v>-13.5841</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.4451</v>
+        <v>-3.445099999999999</v>
       </c>
       <c r="I22" t="n">
         <v>-10.1392</v>
       </c>
       <c r="J22" t="n">
-        <v>2.631200000000001</v>
+        <v>2.6312</v>
       </c>
       <c r="K22" t="n">
         <v>4.145300000000001</v>
@@ -2170,16 +2170,16 @@
         <v>21.2385</v>
       </c>
       <c r="S22" t="n">
-        <v>5.2399</v>
+        <v>5.9295</v>
       </c>
       <c r="T22" t="n">
-        <v>5.651199999999999</v>
+        <v>5.6512</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4113</v>
+        <v>0.2783</v>
       </c>
       <c r="V22" t="n">
-        <v>0.04270000000000085</v>
+        <v>0.04269999999999996</v>
       </c>
       <c r="W22" t="n">
         <v>4.8255</v>
